--- a/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
+++ b/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE283DB-3C49-46A4-9DB1-7F5F063C2B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE0B40F-2D26-4B8D-8535-F98D14E5385E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
-    <sheet name="FHEAT_MANHEAT_10_30" sheetId="1" r:id="rId1"/>
+    <sheet name="BHEAT_MANHEAT_10_20" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,13 +104,13 @@
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>UC_FHEAT_MANHEAT_MAX</t>
-  </si>
-  <si>
     <t>FHEAT</t>
   </si>
   <si>
-    <t>Maximum use of ELC in Furnace</t>
+    <t>UC_BHEAT_MANHEAT_10_20</t>
+  </si>
+  <si>
+    <t>Minimum use of ELC in Boiler</t>
   </si>
 </sst>
 </file>
@@ -694,13 +694,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>21</v>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -732,13 +732,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -756,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="M7">
         <v>0</v>

--- a/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
+++ b/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE0B40F-2D26-4B8D-8535-F98D14E5385E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873E5920-2454-4C61-A74E-576DD80972AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
     <sheet name="BHEAT_MANHEAT_10_20" sheetId="1" r:id="rId1"/>
@@ -104,13 +104,13 @@
     <t>MANHEAT</t>
   </si>
   <si>
-    <t>FHEAT</t>
-  </si>
-  <si>
     <t>UC_BHEAT_MANHEAT_10_20</t>
   </si>
   <si>
     <t>Minimum use of ELC in Boiler</t>
+  </si>
+  <si>
+    <t>BHEAT</t>
   </si>
 </sst>
 </file>
@@ -621,7 +621,8 @@
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" customWidth="1"/>
     <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -694,13 +695,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
         <v>21</v>
@@ -727,18 +728,18 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -765,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
+++ b/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873E5920-2454-4C61-A74E-576DD80972AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425BCAEB-A399-4599-A999-F7DB302D2138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
   <sheets>
     <sheet name="BHEAT_MANHEAT_10_20" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>UC_COMPRD</t>
   </si>
   <si>
-    <t>HEAT</t>
-  </si>
-  <si>
     <t>MANHEAT</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>BHEAT</t>
+  </si>
+  <si>
+    <t>DMD</t>
   </si>
 </sst>
 </file>
@@ -695,16 +695,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
       </c>
       <c r="H6" t="s">
         <v>19</v>
@@ -728,21 +728,21 @@
         <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>19</v>
@@ -766,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
+++ b/SuppXLS/Scen_UC_BHEAT_MANHEAT_10_20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425BCAEB-A399-4599-A999-F7DB302D2138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6BFD81-A9AD-440D-A6F0-D3085D93B9FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{12993743-A3C9-4B22-8ADD-D2910F70577E}"/>
   </bookViews>
@@ -719,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="M7">
         <v>0</v>
